--- a/memo/理想出力.xlsx
+++ b/memo/理想出力.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.uehara\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.uehara\Documents\workspace\line-to-mora-311\memo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B731C1-2550-4219-A15A-5244FF3D2047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69297DC9-EE4F-4CAC-9A7E-B93613B1C423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A49E74DE-CD4D-4775-BC49-68CBF478B299}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="最終出力例" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_000" localSheetId="0">最終出力例!$B$2:$D$106</definedName>
+    <definedName name="_000" localSheetId="0">最終出力例!$C$2:$E$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
   <si>
     <t>無添加</t>
   </si>
@@ -265,6 +265,25 @@
   <si>
     <t>モーラエンドタイム(s)</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>slice ID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>duration(s)</t>
+  </si>
+  <si>
+    <t>rms</t>
+  </si>
+  <si>
+    <t>f0(Hz)</t>
+  </si>
+  <si>
+    <t>spectral_centroid(Hz)</t>
+  </si>
+  <si>
+    <t>zcr</t>
   </si>
 </sst>
 </file>
@@ -679,1317 +698,2423 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E480911E-C408-42EA-9AB4-B02D2B8E524C}">
-  <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="13.5" customWidth="1"/>
-    <col min="2" max="2" width="9.796875" customWidth="1"/>
-    <col min="3" max="3" width="20.09765625" customWidth="1"/>
-    <col min="4" max="4" width="25.69921875" customWidth="1"/>
-    <col min="5" max="5" width="10.69921875" customWidth="1"/>
-    <col min="6" max="6" width="9.09765625" customWidth="1"/>
-    <col min="7" max="7" width="22.3984375" customWidth="1"/>
-    <col min="8" max="8" width="23.5" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:N62"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>1.61</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>1.17</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" s="1"/>
+      <c r="J2" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K2" s="1">
+        <v>3.1570000000000001E-2</v>
+      </c>
+      <c r="L2" s="1">
+        <v>111.09</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1571.44</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1.0670000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1">
         <v>2</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>1.17</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>1.24</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="1"/>
+      <c r="J3" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K3" s="1">
+        <v>6.6860000000000003E-2</v>
+      </c>
+      <c r="L3" s="1">
+        <v>120.25</v>
+      </c>
+      <c r="M3" s="1">
+        <v>2646.28</v>
+      </c>
+      <c r="N3" s="1">
+        <v>1.814E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1">
         <v>3</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>1.24</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>1.39</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="1"/>
+      <c r="J4" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="K4" s="1">
+        <v>8.8010000000000005E-2</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>3858.61</v>
+      </c>
+      <c r="N4" s="1">
+        <v>9.9080000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1">
         <v>4</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>1.39</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="1"/>
+      <c r="J5" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="K5" s="1">
+        <v>3.526E-2</v>
+      </c>
+      <c r="L5" s="1">
+        <v>191.83</v>
+      </c>
+      <c r="M5" s="1">
+        <v>2377.5100000000002</v>
+      </c>
+      <c r="N5" s="1">
+        <v>2.4369999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="1">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1">
         <v>5</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>1.5</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>1.61</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J6" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="K6" s="1">
+        <v>3.8559999999999997E-2</v>
+      </c>
+      <c r="L6" s="1">
+        <v>154.47999999999999</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2512.42</v>
+      </c>
+      <c r="N6" s="1">
+        <v>4.614E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="1">
+      <c r="D7" s="1">
         <v>1.61</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>1.73</v>
       </c>
-      <c r="E7" s="1">
-        <v>6</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
         <v>1.61</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>1.73</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J7" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="K7" s="1">
+        <v>6.207E-2</v>
+      </c>
+      <c r="L7" s="1">
+        <v>113.76</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1815.14</v>
+      </c>
+      <c r="N7" s="1">
+        <v>2.5919999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="1">
+      <c r="D8" s="1">
         <v>1.73</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>2.0499999999999998</v>
       </c>
-      <c r="E8" s="1">
-        <v>7</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>1.73</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>1.88</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="1"/>
+      <c r="J8" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="K8" s="1">
+        <v>4.8779999999999997E-2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>109.2</v>
+      </c>
+      <c r="M8" s="1">
+        <v>4800.37</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0.17435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1">
-        <v>8</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>1.88</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>1.98</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="1"/>
+      <c r="J9" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>7.1929999999999994E-2</v>
+      </c>
+      <c r="L9" s="1">
+        <v>125.53</v>
+      </c>
+      <c r="M9" s="1">
+        <v>2212.29</v>
+      </c>
+      <c r="N9" s="1">
+        <v>3.7600000000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="1">
-        <v>9</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>1.98</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>2.0499999999999998</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J10" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K10" s="1">
+        <v>5.3260000000000002E-2</v>
+      </c>
+      <c r="L10" s="1">
+        <v>184.91</v>
+      </c>
+      <c r="M10" s="1">
+        <v>2243.7399999999998</v>
+      </c>
+      <c r="N10" s="1">
+        <v>2.623E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
         <v>4</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="1">
+      <c r="D11" s="1">
         <v>2.0499999999999998</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>2.2400000000000002</v>
       </c>
-      <c r="E11" s="1">
-        <v>10</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>2.0499999999999998</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>2.13</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="1"/>
+      <c r="J11" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="K11" s="1">
+        <v>6.0339999999999998E-2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>198.13</v>
+      </c>
+      <c r="M11" s="1">
+        <v>2780.32</v>
+      </c>
+      <c r="N11" s="1">
+        <v>3.4950000000000002E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="1">
-        <v>11</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>2.13</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>2.2400000000000002</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J12" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="K12" s="1">
+        <v>5.6579999999999998E-2</v>
+      </c>
+      <c r="L12" s="1">
+        <v>192.09</v>
+      </c>
+      <c r="M12" s="1">
+        <v>2292.71</v>
+      </c>
+      <c r="N12" s="1">
+        <v>3.2230000000000002E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
         <v>5</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="1">
+      <c r="D13" s="1">
         <v>2.2400000000000002</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>2.62</v>
       </c>
-      <c r="E13" s="1">
-        <v>12</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>2.2400000000000002</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>2.39</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="1"/>
+      <c r="J13" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="K13" s="1">
+        <v>4.5249999999999999E-2</v>
+      </c>
+      <c r="L13" s="1">
+        <v>190.82</v>
+      </c>
+      <c r="M13" s="1">
+        <v>5745.18</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0.20635999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="1">
-        <v>13</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>2.39</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>2.56</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" s="1"/>
+      <c r="J14" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="K14" s="1">
+        <v>2.3019999999999999E-2</v>
+      </c>
+      <c r="L14" s="1">
+        <v>174.43</v>
+      </c>
+      <c r="M14" s="1">
+        <v>3132.43</v>
+      </c>
+      <c r="N14" s="1">
+        <v>5.6410000000000002E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="1">
-        <v>14</v>
-      </c>
-      <c r="F15" s="1" t="s">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>3</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>2.56</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>2.62</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J15" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="K15" s="1">
+        <v>6.2619999999999995E-2</v>
+      </c>
+      <c r="L15" s="1">
+        <v>143.22999999999999</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1758.07</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1.082E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
         <v>6</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="1">
+      <c r="D16" s="1">
         <v>2.62</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="1">
         <v>2.91</v>
       </c>
-      <c r="E16" s="1">
-        <v>15</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>2.62</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>2.72</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A17" s="1"/>
+      <c r="J16" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>5.969E-2</v>
+      </c>
+      <c r="L16" s="1">
+        <v>135.9</v>
+      </c>
+      <c r="M16" s="1">
+        <v>2322.1799999999998</v>
+      </c>
+      <c r="N16" s="1">
+        <v>3.2770000000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="1">
-        <v>16</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>2.72</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <v>2.91</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J17" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="K17" s="1">
+        <v>6.6339999999999996E-2</v>
+      </c>
+      <c r="L17" s="1">
+        <v>134</v>
+      </c>
+      <c r="M17" s="1">
+        <v>2326.4899999999998</v>
+      </c>
+      <c r="N17" s="1">
+        <v>5.6300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
         <v>7</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="1">
+      <c r="D18" s="1">
         <v>2.98</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="1">
         <v>3.09</v>
       </c>
-      <c r="E18" s="1">
-        <v>17</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>2.98</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <v>3.05</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J18" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K18" s="1">
+        <v>2.155E-2</v>
+      </c>
+      <c r="L18" s="1">
+        <v>113.15</v>
+      </c>
+      <c r="M18" s="1">
+        <v>1731.6</v>
+      </c>
+      <c r="N18" s="1">
+        <v>6.4200000000000004E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
         <v>8</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="1">
+      <c r="D19" s="1">
         <v>3.09</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="1">
         <v>3.89</v>
       </c>
-      <c r="E19" s="1">
-        <v>18</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>3.05</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <v>3.42</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A20" s="1"/>
+      <c r="J19" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0.10934000000000001</v>
+      </c>
+      <c r="L19" s="1">
+        <v>179.28</v>
+      </c>
+      <c r="M19" s="1">
+        <v>2656.78</v>
+      </c>
+      <c r="N19" s="1">
+        <v>4.6050000000000001E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="1">
-        <v>19</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="E20" s="1"/>
+      <c r="F20" s="1">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>3.42</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <v>3.56</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A21" s="1"/>
+      <c r="J20" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K20" s="1">
+        <v>3.9719999999999998E-2</v>
+      </c>
+      <c r="L20" s="1">
+        <v>164.57</v>
+      </c>
+      <c r="M20" s="1">
+        <v>3939.72</v>
+      </c>
+      <c r="N20" s="1">
+        <v>4.879E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="1">
-        <v>20</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="E21" s="1"/>
+      <c r="F21" s="1">
+        <v>3</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>3.56</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <v>3.76</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A22" s="1"/>
+      <c r="J21" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="K21" s="1">
+        <v>3.9019999999999999E-2</v>
+      </c>
+      <c r="L21" s="1">
+        <v>163.33000000000001</v>
+      </c>
+      <c r="M21" s="1">
+        <v>6011.45</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0.21693000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="1">
-        <v>21</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="E22" s="1"/>
+      <c r="F22" s="1">
+        <v>4</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>3.76</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <v>3.89</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J22" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1.3650000000000001E-2</v>
+      </c>
+      <c r="L22" s="1">
+        <v>148.94</v>
+      </c>
+      <c r="M22" s="1">
+        <v>1879.57</v>
+      </c>
+      <c r="N22" s="1">
+        <v>2.6120000000000001E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
         <v>9</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="1">
+      <c r="D23" s="1">
         <v>5.01</v>
       </c>
-      <c r="D23" s="1">
+      <c r="E23" s="1">
         <v>5.39</v>
       </c>
-      <c r="E23" s="1">
-        <v>22</v>
-      </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>5.01</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <v>5.17</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A24" s="1"/>
+      <c r="J23" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="K23" s="1">
+        <v>8.5059999999999997E-2</v>
+      </c>
+      <c r="L23" s="1">
+        <v>139.21</v>
+      </c>
+      <c r="M23" s="1">
+        <v>2994.17</v>
+      </c>
+      <c r="N23" s="1">
+        <v>6.0510000000000001E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="1">
-        <v>23</v>
-      </c>
-      <c r="F24" s="1" t="s">
+      <c r="E24" s="1"/>
+      <c r="F24" s="1">
+        <v>2</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <v>5.17</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <v>5.35</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A25" s="1"/>
+      <c r="J24" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="K24" s="1">
+        <v>4.7919999999999997E-2</v>
+      </c>
+      <c r="L24" s="1">
+        <v>205.06</v>
+      </c>
+      <c r="M24" s="1">
+        <v>3345.49</v>
+      </c>
+      <c r="N24" s="1">
+        <v>6.4909999999999995E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="1">
-        <v>24</v>
-      </c>
-      <c r="F25" s="1" t="s">
+      <c r="E25" s="1"/>
+      <c r="F25" s="1">
+        <v>3</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <v>5.35</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <v>5.39</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J25" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K25" s="1">
+        <v>3.0370000000000001E-2</v>
+      </c>
+      <c r="L25" s="1">
+        <v>213.13</v>
+      </c>
+      <c r="M25" s="1">
+        <v>2502.3000000000002</v>
+      </c>
+      <c r="N25" s="1">
+        <v>2.954E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
         <v>10</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="1">
+      <c r="D26" s="1">
         <v>5.39</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E26" s="1">
         <v>5.51</v>
       </c>
-      <c r="E26" s="1">
-        <v>25</v>
-      </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="1">
         <v>1</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
         <v>5.39</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <v>5.51</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J26" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="K26" s="1">
+        <v>5.9180000000000003E-2</v>
+      </c>
+      <c r="L26" s="1">
+        <v>201.82</v>
+      </c>
+      <c r="M26" s="1">
+        <v>2844.64</v>
+      </c>
+      <c r="N26" s="1">
+        <v>4.9979999999999997E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
         <v>11</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="1">
+      <c r="D27" s="1">
         <v>5.51</v>
       </c>
-      <c r="D27" s="1">
+      <c r="E27" s="1">
         <v>5.81</v>
       </c>
-      <c r="E27" s="1">
-        <v>26</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="1">
+      <c r="H27" s="1">
         <v>5.51</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <v>5.63</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A28" s="1"/>
+      <c r="J27" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="K27" s="1">
+        <v>4.657E-2</v>
+      </c>
+      <c r="L27" s="1">
+        <v>187.56</v>
+      </c>
+      <c r="M27" s="1">
+        <v>2663.27</v>
+      </c>
+      <c r="N27" s="1">
+        <v>3.1559999999999998E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="1">
-        <v>27</v>
-      </c>
-      <c r="F28" s="1" t="s">
+      <c r="E28" s="1"/>
+      <c r="F28" s="1">
+        <v>2</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G28" s="1">
+      <c r="H28" s="1">
         <v>5.63</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <v>5.68</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A29" s="1"/>
+      <c r="J28" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="K28" s="1">
+        <v>2.4719999999999999E-2</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>6285.81</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0.19424</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="1">
-        <v>28</v>
-      </c>
-      <c r="F29" s="1" t="s">
+      <c r="E29" s="1"/>
+      <c r="F29" s="1">
+        <v>3</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>5.68</v>
       </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
         <v>5.77</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A30" s="1"/>
+      <c r="J29" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="K29" s="1">
+        <v>7.9900000000000006E-3</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>8301.93</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0.30164000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="1">
-        <v>29</v>
-      </c>
-      <c r="F30" s="1" t="s">
+      <c r="E30" s="1"/>
+      <c r="F30" s="1">
+        <v>4</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <v>5.77</v>
       </c>
-      <c r="H30" s="1">
+      <c r="I30" s="1">
         <v>5.81</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J30" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K30" s="1">
+        <v>4.3610000000000003E-2</v>
+      </c>
+      <c r="L30" s="1">
+        <v>193.75</v>
+      </c>
+      <c r="M30" s="1">
+        <v>3892.17</v>
+      </c>
+      <c r="N30" s="1">
+        <v>4.3580000000000001E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1">
         <v>12</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="1">
+      <c r="D31" s="1">
         <v>5.81</v>
       </c>
-      <c r="D31" s="1">
+      <c r="E31" s="1">
         <v>6.17</v>
       </c>
-      <c r="E31" s="1">
-        <v>30</v>
-      </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G31" s="1">
+      <c r="H31" s="1">
         <v>5.81</v>
       </c>
-      <c r="H31" s="1">
+      <c r="I31" s="1">
         <v>5.9</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A32" s="1"/>
+      <c r="J31" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1.8950000000000002E-2</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>8186.7</v>
+      </c>
+      <c r="N31" s="1">
+        <v>0.35894999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="1">
-        <v>31</v>
-      </c>
-      <c r="F32" s="1" t="s">
+      <c r="E32" s="1"/>
+      <c r="F32" s="1">
+        <v>2</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G32" s="1">
+      <c r="H32" s="1">
         <v>5.9</v>
       </c>
-      <c r="H32" s="1">
+      <c r="I32" s="1">
         <v>6.02</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A33" s="1"/>
+      <c r="J32" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="K32" s="1">
+        <v>5.5469999999999998E-2</v>
+      </c>
+      <c r="L32" s="1">
+        <v>198.18</v>
+      </c>
+      <c r="M32" s="1">
+        <v>2668.38</v>
+      </c>
+      <c r="N32" s="1">
+        <v>2.6859999999999998E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="1">
-        <v>32</v>
-      </c>
-      <c r="F33" s="1" t="s">
+      <c r="E33" s="1"/>
+      <c r="F33" s="1">
+        <v>3</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G33" s="1">
+      <c r="H33" s="1">
         <v>6.02</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <v>6.06</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A34" s="1"/>
+      <c r="J33" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1.3849999999999999E-2</v>
+      </c>
+      <c r="L33" s="1">
+        <v>153.79</v>
+      </c>
+      <c r="M33" s="1">
+        <v>2550.2399999999998</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1.0500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="1">
-        <v>33</v>
-      </c>
-      <c r="F34" s="1" t="s">
+      <c r="E34" s="1"/>
+      <c r="F34" s="1">
+        <v>4</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G34" s="1">
+      <c r="H34" s="1">
         <v>6.06</v>
       </c>
-      <c r="H34" s="1">
+      <c r="I34" s="1">
         <v>6.12</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A35" s="1"/>
+      <c r="J34" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="K34" s="1">
+        <v>6.1069999999999999E-2</v>
+      </c>
+      <c r="L34" s="1">
+        <v>150.75</v>
+      </c>
+      <c r="M34" s="1">
+        <v>2602.6</v>
+      </c>
+      <c r="N34" s="1">
+        <v>1.8069999999999999E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="1">
-        <v>34</v>
-      </c>
-      <c r="F35" s="1" t="s">
+      <c r="E35" s="1"/>
+      <c r="F35" s="1">
+        <v>5</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G35" s="1">
+      <c r="H35" s="1">
         <v>6.12</v>
       </c>
-      <c r="H35" s="1">
+      <c r="I35" s="1">
         <v>6.17</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J35" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="K35" s="1">
+        <v>6.3570000000000002E-2</v>
+      </c>
+      <c r="L35" s="1">
+        <v>131</v>
+      </c>
+      <c r="M35" s="1">
+        <v>2189.41</v>
+      </c>
+      <c r="N35" s="1">
+        <v>8.5900000000000004E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
         <v>13</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="1">
+      <c r="D36" s="1">
         <v>6.17</v>
       </c>
-      <c r="D36" s="1">
+      <c r="E36" s="1">
         <v>6.27</v>
       </c>
-      <c r="E36" s="1">
-        <v>35</v>
-      </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="1">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G36" s="1">
+      <c r="H36" s="1">
         <v>6.17</v>
       </c>
-      <c r="H36" s="1">
+      <c r="I36" s="1">
         <v>6.27</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J36" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K36" s="1">
+        <v>4.3639999999999998E-2</v>
+      </c>
+      <c r="L36" s="1">
+        <v>109.87</v>
+      </c>
+      <c r="M36" s="1">
+        <v>2436.0500000000002</v>
+      </c>
+      <c r="N36" s="1">
+        <v>3.1579999999999997E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1">
         <v>14</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="1">
+      <c r="D37" s="1">
         <v>6.27</v>
       </c>
-      <c r="D37" s="1">
+      <c r="E37" s="1">
         <v>6.79</v>
       </c>
-      <c r="E37" s="1">
-        <v>36</v>
-      </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G37" s="1">
+      <c r="H37" s="1">
         <v>6.27</v>
       </c>
-      <c r="H37" s="1">
+      <c r="I37" s="1">
         <v>6.35</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A38" s="1"/>
+      <c r="J37" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="K37" s="1">
+        <v>9.7800000000000005E-3</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>3297.75</v>
+      </c>
+      <c r="N37" s="1">
+        <v>6.3130000000000006E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="1">
-        <v>37</v>
-      </c>
-      <c r="F38" s="1" t="s">
+      <c r="E38" s="1"/>
+      <c r="F38" s="1">
+        <v>2</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G38" s="1">
+      <c r="H38" s="1">
         <v>6.35</v>
       </c>
-      <c r="H38" s="1">
+      <c r="I38" s="1">
         <v>6.43</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A39" s="1"/>
+      <c r="J38" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="K38" s="1">
+        <v>3.7399999999999998E-3</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>2645.29</v>
+      </c>
+      <c r="N38" s="1">
+        <v>1.542E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="1">
-        <v>38</v>
-      </c>
-      <c r="F39" s="1" t="s">
+      <c r="E39" s="1"/>
+      <c r="F39" s="1">
+        <v>3</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G39" s="1">
+      <c r="H39" s="1">
         <v>6.43</v>
       </c>
-      <c r="H39" s="1">
+      <c r="I39" s="1">
         <v>6.47</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A40" s="1"/>
+      <c r="J39" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K39" s="1">
+        <v>4.8180000000000001E-2</v>
+      </c>
+      <c r="L39" s="1">
+        <v>126.72</v>
+      </c>
+      <c r="M39" s="1">
+        <v>1886.91</v>
+      </c>
+      <c r="N39" s="1">
+        <v>1.038E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="1">
-        <v>39</v>
-      </c>
-      <c r="F40" s="1" t="s">
+      <c r="E40" s="1"/>
+      <c r="F40" s="1">
+        <v>4</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G40" s="1">
+      <c r="H40" s="1">
         <v>6.47</v>
       </c>
-      <c r="H40" s="1">
+      <c r="I40" s="1">
         <v>6.59</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A41" s="1"/>
+      <c r="J40" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="K40" s="1">
+        <v>6.6390000000000005E-2</v>
+      </c>
+      <c r="L40" s="1">
+        <v>142.13</v>
+      </c>
+      <c r="M40" s="1">
+        <v>2005.15</v>
+      </c>
+      <c r="N40" s="1">
+        <v>2.4369999999999999E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1">
-        <v>40</v>
-      </c>
-      <c r="F41" s="1" t="s">
+      <c r="E41" s="1"/>
+      <c r="F41" s="1">
+        <v>5</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G41" s="1">
+      <c r="H41" s="1">
         <v>6.59</v>
       </c>
-      <c r="H41" s="1">
+      <c r="I41" s="1">
         <v>6.7</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A42" s="1"/>
+      <c r="J41" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="K41" s="1">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="L41" s="1">
+        <v>146.77000000000001</v>
+      </c>
+      <c r="M41" s="1">
+        <v>2294.06</v>
+      </c>
+      <c r="N41" s="1">
+        <v>2.563E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="1">
-        <v>41</v>
-      </c>
-      <c r="F42" s="1" t="s">
+      <c r="E42" s="1"/>
+      <c r="F42" s="1">
+        <v>6</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G42" s="1">
+      <c r="H42" s="1">
         <v>6.7</v>
       </c>
-      <c r="H42" s="1">
+      <c r="I42" s="1">
         <v>6.74</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A43" s="1"/>
+      <c r="J42" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K42" s="1">
+        <v>2.8379999999999999E-2</v>
+      </c>
+      <c r="L42" s="1">
+        <v>131.77000000000001</v>
+      </c>
+      <c r="M42" s="1">
+        <v>2305.86</v>
+      </c>
+      <c r="N42" s="1">
+        <v>1.9650000000000001E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="1">
-        <v>42</v>
-      </c>
-      <c r="F43" s="1" t="s">
+      <c r="E43" s="1"/>
+      <c r="F43" s="1">
+        <v>7</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G43" s="1">
+      <c r="H43" s="1">
         <v>6.74</v>
       </c>
-      <c r="H43" s="1">
+      <c r="I43" s="1">
         <v>6.79</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J43" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="K43" s="1">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="L43" s="1">
+        <v>126.78</v>
+      </c>
+      <c r="M43" s="1">
+        <v>2488.3200000000002</v>
+      </c>
+      <c r="N43" s="1">
+        <v>1.4160000000000001E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
         <v>15</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="1">
+      <c r="D44" s="1">
         <v>6.79</v>
       </c>
-      <c r="D44" s="1">
+      <c r="E44" s="1">
         <v>7.12</v>
       </c>
-      <c r="E44" s="1">
-        <v>43</v>
-      </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G44" s="1">
+      <c r="H44" s="1">
         <v>6.79</v>
       </c>
-      <c r="H44" s="1">
+      <c r="I44" s="1">
         <v>6.91</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A45" s="1"/>
+      <c r="J44" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="K44" s="1">
+        <v>2.801E-2</v>
+      </c>
+      <c r="L44" s="1">
+        <v>109.6</v>
+      </c>
+      <c r="M44" s="1">
+        <v>2278.66</v>
+      </c>
+      <c r="N44" s="1">
+        <v>2.8500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="1">
-        <v>44</v>
-      </c>
-      <c r="F45" s="1" t="s">
+      <c r="E45" s="1"/>
+      <c r="F45" s="1">
+        <v>2</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G45" s="1">
+      <c r="H45" s="1">
         <v>6.91</v>
       </c>
-      <c r="H45" s="1">
+      <c r="I45" s="1">
         <v>7.12</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J45" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="K45" s="1">
+        <v>6.3070000000000001E-2</v>
+      </c>
+      <c r="L45" s="1">
+        <v>97.31</v>
+      </c>
+      <c r="M45" s="1">
+        <v>1787.26</v>
+      </c>
+      <c r="N45" s="1">
+        <v>2.639E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
         <v>16</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="1">
+      <c r="D46" s="1">
         <v>7.31</v>
       </c>
-      <c r="D46" s="1">
+      <c r="E46" s="1">
         <v>7.6</v>
       </c>
-      <c r="E46" s="1">
-        <v>45</v>
-      </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="1">
+        <v>1</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G46" s="1">
+      <c r="H46" s="1">
         <v>7.31</v>
       </c>
-      <c r="H46" s="1">
+      <c r="I46" s="1">
         <v>7.46</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A47" s="1"/>
+      <c r="J46" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="K46" s="1">
+        <v>5.2789999999999997E-2</v>
+      </c>
+      <c r="L46" s="1">
+        <v>126.08</v>
+      </c>
+      <c r="M46" s="1">
+        <v>2511.2399999999998</v>
+      </c>
+      <c r="N46" s="1">
+        <v>3.2230000000000002E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="1">
-        <v>46</v>
-      </c>
-      <c r="F47" s="1" t="s">
+      <c r="E47" s="1"/>
+      <c r="F47" s="1">
+        <v>2</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G47" s="1">
+      <c r="H47" s="1">
         <v>7.46</v>
       </c>
-      <c r="H47" s="1">
+      <c r="I47" s="1">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J47" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K47" s="1">
+        <v>8.0979999999999996E-2</v>
+      </c>
+      <c r="L47" s="1">
+        <v>119.81</v>
+      </c>
+      <c r="M47" s="1">
+        <v>1907.6</v>
+      </c>
+      <c r="N47" s="1">
+        <v>1.273E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1">
         <v>17</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="1">
+      <c r="D48" s="1">
         <v>7.6</v>
       </c>
-      <c r="D48" s="1">
+      <c r="E48" s="1">
         <v>7.75</v>
       </c>
-      <c r="E48" s="1">
-        <v>47</v>
-      </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="1">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G48" s="1">
+      <c r="H48" s="1">
         <v>7.6</v>
       </c>
-      <c r="H48" s="1">
+      <c r="I48" s="1">
         <v>7.75</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J48" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="K48" s="1">
+        <v>4.1180000000000001E-2</v>
+      </c>
+      <c r="L48" s="1">
+        <v>91</v>
+      </c>
+      <c r="M48" s="1">
+        <v>1998.59</v>
+      </c>
+      <c r="N48" s="1">
+        <v>1.1270000000000001E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1">
         <v>18</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="1">
+      <c r="D49" s="1">
         <v>7.75</v>
       </c>
-      <c r="D49" s="1">
+      <c r="E49" s="1">
         <v>8.23</v>
       </c>
-      <c r="E49" s="1">
-        <v>48</v>
-      </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="1">
+        <v>1</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G49" s="1">
+      <c r="H49" s="1">
         <v>7.75</v>
       </c>
-      <c r="H49" s="1">
+      <c r="I49" s="1">
         <v>7.9</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A50" s="1"/>
+      <c r="J49" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="K49" s="1">
+        <v>4.6420000000000003E-2</v>
+      </c>
+      <c r="L49" s="1">
+        <v>93.74</v>
+      </c>
+      <c r="M49" s="1">
+        <v>1230.1199999999999</v>
+      </c>
+      <c r="N49" s="1">
+        <v>7.2100000000000003E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="1">
-        <v>49</v>
-      </c>
-      <c r="F50" s="1" t="s">
+      <c r="E50" s="1"/>
+      <c r="F50" s="1">
+        <v>2</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G50" s="1">
+      <c r="H50" s="1">
         <v>7.9</v>
       </c>
-      <c r="H50" s="1">
+      <c r="I50" s="1">
         <v>7.94</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A51" s="1"/>
+      <c r="J50" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="K50" s="1">
+        <v>3.9109999999999999E-2</v>
+      </c>
+      <c r="L50" s="1">
+        <v>100.03</v>
+      </c>
+      <c r="M50" s="1">
+        <v>2065.9499999999998</v>
+      </c>
+      <c r="N50" s="1">
+        <v>5.4900000000000001E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="1">
-        <v>50</v>
-      </c>
-      <c r="F51" s="1" t="s">
+      <c r="E51" s="1"/>
+      <c r="F51" s="1">
+        <v>3</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G51" s="1">
+      <c r="H51" s="1">
         <v>7.94</v>
       </c>
-      <c r="H51" s="1">
+      <c r="I51" s="1">
         <v>8.1300000000000008</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A52" s="1"/>
+      <c r="J51" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="K51" s="1">
+        <v>6.6049999999999998E-2</v>
+      </c>
+      <c r="L51" s="1">
+        <v>167.24</v>
+      </c>
+      <c r="M51" s="1">
+        <v>1801.71</v>
+      </c>
+      <c r="N51" s="1">
+        <v>1.66E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="1">
-        <v>51</v>
-      </c>
-      <c r="F52" s="1" t="s">
+      <c r="E52" s="1"/>
+      <c r="F52" s="1">
+        <v>4</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G52" s="1">
+      <c r="H52" s="1">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H52" s="1">
+      <c r="I52" s="1">
         <v>8.23</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J52" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K52" s="1">
+        <v>6.2630000000000005E-2</v>
+      </c>
+      <c r="L52" s="1">
+        <v>171.63</v>
+      </c>
+      <c r="M52" s="1">
+        <v>1985.41</v>
+      </c>
+      <c r="N52" s="1">
+        <v>1.4760000000000001E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1">
         <v>19</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="1">
+      <c r="D53" s="1">
         <v>8.23</v>
       </c>
-      <c r="D53" s="1">
+      <c r="E53" s="1">
         <v>8.32</v>
       </c>
-      <c r="E53" s="1">
-        <v>52</v>
-      </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="1">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G53" s="1">
+      <c r="H53" s="1">
         <v>8.23</v>
       </c>
-      <c r="H53" s="1">
+      <c r="I53" s="1">
         <v>8.32</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J53" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="K53" s="1">
+        <v>5.475E-2</v>
+      </c>
+      <c r="L53" s="1">
+        <v>157.37</v>
+      </c>
+      <c r="M53" s="1">
+        <v>1932.93</v>
+      </c>
+      <c r="N53" s="1">
+        <v>3.6929999999999998E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1">
         <v>20</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="1">
+      <c r="D54" s="1">
         <v>8.32</v>
       </c>
-      <c r="D54" s="1">
+      <c r="E54" s="1">
         <v>8.73</v>
       </c>
-      <c r="E54" s="1">
+      <c r="F54" s="1">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G54" s="1">
+      <c r="H54" s="1">
         <v>8.32</v>
       </c>
-      <c r="H54" s="1">
+      <c r="I54" s="1">
         <v>8.39</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A55" s="1"/>
+      <c r="J54" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K54" s="1">
+        <v>4.0689999999999997E-2</v>
+      </c>
+      <c r="L54" s="1">
+        <v>139.74</v>
+      </c>
+      <c r="M54" s="1">
+        <v>2122.37</v>
+      </c>
+      <c r="N54" s="1">
+        <v>2.9989999999999999E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="1">
-        <v>54</v>
-      </c>
-      <c r="F55" s="1" t="s">
+      <c r="E55" s="1"/>
+      <c r="F55" s="1">
+        <v>2</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G55" s="1">
+      <c r="H55" s="1">
         <v>8.39</v>
       </c>
-      <c r="H55" s="1">
+      <c r="I55" s="1">
         <v>8.58</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A56" s="1"/>
+      <c r="J55" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="K55" s="1">
+        <v>2.6089999999999999E-2</v>
+      </c>
+      <c r="L55" s="1">
+        <v>129.51</v>
+      </c>
+      <c r="M55" s="1">
+        <v>3234.44</v>
+      </c>
+      <c r="N55" s="1">
+        <v>5.5579999999999997E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
-      <c r="E56" s="1">
-        <v>55</v>
-      </c>
-      <c r="F56" s="1" t="s">
+      <c r="E56" s="1"/>
+      <c r="F56" s="1">
+        <v>3</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G56" s="1">
+      <c r="H56" s="1">
         <v>8.58</v>
       </c>
-      <c r="H56" s="1">
+      <c r="I56" s="1">
         <v>8.73</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J56" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="K56" s="1">
+        <v>2.955E-2</v>
+      </c>
+      <c r="L56" s="1">
+        <v>224.59</v>
+      </c>
+      <c r="M56" s="1">
+        <v>2352.69</v>
+      </c>
+      <c r="N56" s="1">
+        <v>4.4170000000000001E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1">
         <v>21</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="1">
+      <c r="D57" s="1">
         <v>9</v>
       </c>
-      <c r="D57" s="1">
+      <c r="E57" s="1">
         <v>9.5500000000000007</v>
       </c>
-      <c r="E57" s="1">
-        <v>56</v>
-      </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="1">
+        <v>1</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="1">
+      <c r="H57" s="1">
         <v>9</v>
       </c>
-      <c r="H57" s="1">
+      <c r="I57" s="1">
         <v>9.1</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A58" s="1"/>
+      <c r="J57" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K57" s="1">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>8475.14</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0.31531999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
-      <c r="E58" s="1">
-        <v>57</v>
-      </c>
-      <c r="F58" s="1" t="s">
+      <c r="E58" s="1"/>
+      <c r="F58" s="1">
+        <v>2</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G58" s="1">
+      <c r="H58" s="1">
         <v>9.1</v>
       </c>
-      <c r="H58" s="1">
+      <c r="I58" s="1">
         <v>9.16</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A59" s="1"/>
+      <c r="J58" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="K58" s="1">
+        <v>7.3899999999999999E-3</v>
+      </c>
+      <c r="L58" s="1">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <v>6818.22</v>
+      </c>
+      <c r="N58" s="1">
+        <v>0.15031</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
-      <c r="E59" s="1">
-        <v>58</v>
-      </c>
-      <c r="F59" s="1" t="s">
+      <c r="E59" s="1"/>
+      <c r="F59" s="1">
+        <v>3</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G59" s="1">
+      <c r="H59" s="1">
         <v>9.16</v>
       </c>
-      <c r="H59" s="1">
+      <c r="I59" s="1">
         <v>9.26</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A60" s="1"/>
+      <c r="J59" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K59" s="1">
+        <v>3.0849999999999999E-2</v>
+      </c>
+      <c r="L59" s="1">
+        <v>166.35</v>
+      </c>
+      <c r="M59" s="1">
+        <v>3035.47</v>
+      </c>
+      <c r="N59" s="1">
+        <v>4.0149999999999998E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
-      <c r="E60" s="1">
-        <v>59</v>
-      </c>
-      <c r="F60" s="1" t="s">
+      <c r="E60" s="1"/>
+      <c r="F60" s="1">
+        <v>4</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G60" s="1">
+      <c r="H60" s="1">
         <v>9.26</v>
       </c>
-      <c r="H60" s="1">
+      <c r="I60" s="1">
         <v>9.42</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A61" s="1"/>
+      <c r="J60" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="K60" s="1">
+        <v>6.5290000000000001E-2</v>
+      </c>
+      <c r="L60" s="1">
+        <v>201.85</v>
+      </c>
+      <c r="M60" s="1">
+        <v>2787.68</v>
+      </c>
+      <c r="N60" s="1">
+        <v>3.6760000000000001E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
-      <c r="E61" s="1">
-        <v>60</v>
-      </c>
-      <c r="F61" s="1" t="s">
+      <c r="E61" s="1"/>
+      <c r="F61" s="1">
+        <v>5</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="1">
+      <c r="H61" s="1">
         <v>9.42</v>
       </c>
-      <c r="H61" s="1">
+      <c r="I61" s="1">
         <v>9.5500000000000007</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="J61" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="K61" s="1">
+        <v>4.4380000000000003E-2</v>
+      </c>
+      <c r="L61" s="1">
+        <v>156.43</v>
+      </c>
+      <c r="M61" s="1">
+        <v>2721.84</v>
+      </c>
+      <c r="N61" s="1">
+        <v>5.1429999999999997E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1">
         <v>22</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="1">
+      <c r="D62" s="1">
         <v>9.5500000000000007</v>
       </c>
-      <c r="D62" s="1">
+      <c r="E62" s="1">
         <v>9.67</v>
       </c>
-      <c r="E62" s="1">
-        <v>61</v>
-      </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="1">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G62" s="1">
+      <c r="H62" s="1">
         <v>9.5500000000000007</v>
       </c>
-      <c r="H62" s="1">
+      <c r="I62" s="1">
         <v>9.67</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="K62" s="1">
+        <v>5.2659999999999998E-2</v>
+      </c>
+      <c r="L62" s="1">
+        <v>179.21</v>
+      </c>
+      <c r="M62" s="1">
+        <v>2704.31</v>
+      </c>
+      <c r="N62" s="1">
+        <v>2.384E-2</v>
       </c>
     </row>
   </sheetData>
